--- a/best_tenders.xlsx
+++ b/best_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>687.</t>
+          <t>736.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2003.</t>
+          <t>2017.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>910.</t>
+          <t>959.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/best_tenders.xlsx
+++ b/best_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>736.</t>
+          <t>881.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2017.</t>
+          <t>1914.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>959.</t>
+          <t>1104.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/best_tenders.xlsx
+++ b/best_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>881.</t>
+          <t>1113.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1914.</t>
+          <t>1974.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1104.</t>
+          <t>1322.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/best_tenders.xlsx
+++ b/best_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1113.</t>
+          <t>1424.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1974.</t>
+          <t>2124.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1322.</t>
+          <t>1616.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/best_tenders.xlsx
+++ b/best_tenders.xlsx
@@ -494,45 +494,45 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1424.</t>
+          <t>288.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11-Jun-2026 12:30 PM</t>
+          <t>18-Jun-2026 10:45 AM</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>01-Jul-2026 05:00 PM</t>
+          <t>06-Jul-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>02-Jul-2026 11:00 AM</t>
+          <t>07-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>[Construction of Office Building of State Environment Impact and Assessment Authority (SEIAA) at plot no. IP8 Sector 5B, MDC, Panchkula] [2026711ADBA6 A8AB 4EB9 A315 F80198C0E35D57HHC][2026_HBC_528297_1]</t>
+          <t>[Construction of office Building of Lokayukta, Haryana at Site No.1, Sector-1 Panchkula] [2026372F4AAC 9753 41F7 A0D4 183C890E5A2A616BAR][2026_HRY_529910_1]</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Haryana Board Corporation||Haryana Police Housing Corporation</t>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE Panchkula</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15,39,73,912</t>
+          <t>19,08,13,426</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>153973912</v>
+        <v>190813426</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SY%2FduOAMju2zzhLsQn%2Bgtfg%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SuTrdrCfBLNHknj7WtjrWPQ%3D%3D</t>
         </is>
       </c>
     </row>
@@ -548,49 +548,49 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2124.</t>
+          <t>1578.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>02-Jun-2026 11:00 AM</t>
+          <t>11-Jun-2026 12:30 PM</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>17-Jun-2026 05:00 PM</t>
+          <t>01-Jul-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>18-Jun-2026 03:00 PM</t>
+          <t>02-Jul-2026 11:00 AM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>[Construction of Office Building of DMER PLOT No. IP-1 (P) MDC, Sector-6 Panchkula. (Balance Work).] [2026570C498D 871A 4B85 9F0F ECAEFF719355616BAR][2026_HRY_526032_1]</t>
+          <t>[Construction of Office Building of State Environment Impact and Assessment Authority (SEIAA) at plot no. IP8 Sector 5B, MDC, Panchkula] [2026711ADBA6 A8AB 4EB9 A315 F80198C0E35D57HHC][2026_HBC_528297_1]</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE Panchkula</t>
+          <t>Haryana Board Corporation||Haryana Police Housing Corporation</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9,61,59,224</t>
+          <t>15,39,73,912</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>96159224</v>
+        <v>153973912</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SO8pz50FKGHiM6Kd2v9AG1g%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SY%2FduOAMju2zzhLsQn%2Bgtfg%3D%3D</t>
         </is>
       </c>
     </row>
@@ -610,45 +610,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1616.</t>
+          <t>1898.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10-Jun-2026 05:00 PM</t>
+          <t>02-Jun-2026 11:00 AM</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>18-Jun-2026 03:00 PM</t>
+          <t>01-Jul-2026 05:00 PM</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>18-Jun-2026 03:10 PM</t>
+          <t>02-Jul-2026 03:00 PM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>[Construction of school building in GSSS Dhareru] [20263F49E116 A6A8 4850 98F9 76FBCFD64BD91026SSP][2026_HBC_528054_1]</t>
+          <t>[Construction of Office Building of DMER PLOT No. IP-1 (P) MDC, Sector-6 Panchkula. (Balance Work).] [2026570C498D 871A 4B85 9F0F ECAEFF719355616BAR][2026_HRY_526032_1]</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Haryana Board Corporation||HSSPP Panchkula</t>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE Panchkula</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1,73,65,727</t>
+          <t>9,61,59,224</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>17365727</v>
+        <v>96159224</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SJD%2FD2%2FEIE7Rtc6PfuAfdHA%3D%3D</t>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SO8pz50FKGHiM6Kd2v9AG1g%3D%3D</t>
         </is>
       </c>
     </row>

--- a/best_tenders.xlsx
+++ b/best_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>288.</t>
+          <t>299.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1578.</t>
+          <t>1586.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1898.</t>
+          <t>1902.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/best_tenders.xlsx
+++ b/best_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>299.</t>
+          <t>630.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1586.</t>
+          <t>1814.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1902.</t>
+          <t>2104.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/best_tenders.xlsx
+++ b/best_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>630.</t>
+          <t>635.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1814.</t>
+          <t>1795.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2104.</t>
+          <t>2085.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/best_tenders.xlsx
+++ b/best_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>635.</t>
+          <t>783.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1795.</t>
+          <t>1854.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2085.</t>
+          <t>2128.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/best_tenders.xlsx
+++ b/best_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>783.</t>
+          <t>1017.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1854.</t>
+          <t>1794.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2128.</t>
+          <t>1994.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/best_tenders.xlsx
+++ b/best_tenders.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1017.</t>
+          <t>1138.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1794.</t>
+          <t>1795.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1994.</t>
+          <t>1989.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/best_tenders.xlsx
+++ b/best_tenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,180 +475,6 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>Direct Link</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Best Tender</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Haryana eTenders</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>67</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1138.</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>18-Jun-2026 10:45 AM</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>06-Jul-2026 05:00 PM</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>07-Jul-2026 03:00 PM</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>[Construction of office Building of Lokayukta, Haryana at Site No.1, Sector-1 Panchkula] [2026372F4AAC 9753 41F7 A0D4 183C890E5A2A616BAR][2026_HRY_529910_1]</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE Panchkula</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>19,08,13,426</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
-        <v>190813426</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SuTrdrCfBLNHknj7WtjrWPQ%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Best Tender</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Haryana eTenders</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>67</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>1795.</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>11-Jun-2026 12:30 PM</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>01-Jul-2026 05:00 PM</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>02-Jul-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>[Construction of Office Building of State Environment Impact and Assessment Authority (SEIAA) at plot no. IP8 Sector 5B, MDC, Panchkula] [2026711ADBA6 A8AB 4EB9 A315 F80198C0E35D57HHC][2026_HBC_528297_1]</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Haryana Board Corporation||Haryana Police Housing Corporation</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>15,39,73,912</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
-        <v>153973912</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SY%2FduOAMju2zzhLsQn%2Bgtfg%3D%3D</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Best Tender</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Haryana eTenders</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>62</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1989.</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>02-Jun-2026 11:00 AM</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>01-Jul-2026 05:00 PM</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>02-Jul-2026 03:00 PM</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>[Construction of Office Building of DMER PLOT No. IP-1 (P) MDC, Sector-6 Panchkula. (Balance Work).] [2026570C498D 871A 4B85 9F0F ECAEFF719355616BAR][2026_HRY_526032_1]</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE Panchkula</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>9,61,59,224</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>96159224</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SO8pz50FKGHiM6Kd2v9AG1g%3D%3D</t>
         </is>
       </c>
     </row>

--- a/best_tenders.xlsx
+++ b/best_tenders.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,6 +478,1050 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>117</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1697.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>18-Jun-2026 10:45 AM</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>07-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>[Construction of office Building of Lokayukta, Haryana at Site No.1, Sector-1 Panchkula] [2026372F4AAC 9753 41F7 A0D4 183C890E5A2A616BAR][2026_HRY_529910_1]</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE Panchkula</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>19,08,13,426</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>190813426</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SuTrdrCfBLNHknj7WtjrWPQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>112</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1900.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>02-Jun-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>[Construction of Office Building of DMER PLOT No. IP-1 (P) MDC, Sector-6 Panchkula. (Balance Work).] [2026570C498D 871A 4B85 9F0F ECAEFF719355616BAR][2026_HRY_526032_1]</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Chandigarh||EE Panchkula</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>9,61,59,224</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>96159224</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SO8pz50FKGHiM6Kd2v9AG1g%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Uttarakhand eTenders</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>90</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>261.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 04:15 PM</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 03:30 PM</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>[Construction of Proposed Regional Office Building for Pollution Board at Dehradun.] [962/BRIDCUL/1077/26 Dated 19.06.2026][2026_BRID3_96886_1]</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>MD - BRIDCUL||General Manager (Civil/Project)||PM (Dehradun)||JE</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4,50,46,000</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>45046000</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://uktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SYU8Olh4hsb5k%2FPoIJVb%2FAQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>JK eTenders</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>90</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2118.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 03:15 PM</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 04:00 PM</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>[Construction of Demonstration Rooms (06 nos.) on roof top of third Floor of Main College Building of GMC Kathua (Under Capex Budget 2025-26).] [e-NIT No.PWD/SE/KS/20 of 2026-27 Dated 24-06-2026][2026_PWDJK_313615_1]</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>PWD||CE RandB Jammu||SE RandB Kathua Samba</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2,81,43,000</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>28143000</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://jktenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ShxFWwxuYULc%2Bn9QBbDXZDA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>90</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1766.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>26-Jun-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>[Const of covered auction platfarm 230ftx80ft by Self Supporting Metallic roofing front side of office building at Kums Pratapgarh] [RSAMB/BHILWARA/NIB NO 06/2026-27 ][2026_RSAMB_571264_12]</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>RSAMB||ACE - Zone I||S.E. - Circle Ajmer||Ex.En. - Chittorgarh</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>1,59,20,000</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>15920000</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=ST2YIs%2B7rDVdRUX8DbBYeDA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>90</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1548.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>26-Jun-2026 05:05 PM</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>06-Jul-2026 11:15 AM</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>[Construction of sub division office building at Jalsu, Jaipur.] [E-NIT 02/2026-27][2026_JVVNL_571333_21]</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>JVVNL - CMD||CE(O and M), Jaipur||SE-Civil</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>1,00,00,000</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SlitjipCXcMe89SOZqYq2oQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>75</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1097.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>25-Jun-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 12:00 PM</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[Renovation work for office building of Advocate General Haryana at Chandigarh (Deposite work) of Advocate General Haryana (Balance work)] [2026DDE39FAF 8F82 483C 9A02 6FF9DD62175F270HSV][2026_HBC_531909_1]</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Haryana Board Corporation||HUDA||PKL Division II</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1,98,80,991</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>19880991</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc9eIaeYuAN%2FryxX3743FQg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>65</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1802.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>12-Jun-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>03-Jul-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[Construction of EVM Warehouse Godown at Sector-2 Rohtak] [2026700D3E7D 53FE 43DE 9797 BE9913718D62653BAR][2026_HRY_528819_1]</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Rohtak||EE PD-2 Rohtak</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>10,51,01,701</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>105101701</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sry5YRZyJYErEnc0cX5iBww%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>65</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1540.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>22-Jun-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>15-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>16-Jul-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[Construction of building of...] [2026C9E1FE7F 993F 4754 8589 4DC15137F937645BAR][2026_HRY_530778_1]</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Haryana Government||Engineer-in-Chief PW(B and R) Department||SE Karnal||EE PD-2 Karnal</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>9,55,97,065</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>95597065</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S4di%2FBfHQPp6IR%2FBTk5jLxQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Haryana eTenders</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>65</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2010.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>01-May-2026 03:00 PM</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>13-Jul-2026 05:00 PM</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>14-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>[Construction of building for the Center for Distance and Online Education at 1st floor of building of University Works Department at GJU SandT, Hisar] [20262EB9E91C DD60 44A8 8F26 855DAA2E38B61129GJU][2026_HRY_519090_1]</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Haryana Government||GJUS and T Hisar</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1,58,61,542</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>15861542</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://etenders.hry.nic.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=S7%2B3mMyKcPocPDYXPM0hGCw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>60</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>295.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>23-Jul-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>[Construction of Police Station Building at Savina in district Udaipur] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_4]</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>3,11,00,000</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>31100000</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SLIOzXMySdAgtJmxjwwPIeA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>60</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>294.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>23-Jul-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[Construction of Police station Building at Sadar Bazar under Police Commissionerate Jodhpur] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_3]</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>3,10,24,000</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>31024000</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SR7Njsl%2FDbjyCmTu9Cl1t2g%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>298.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>23-Jul-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[Construction of Police station building at Obri Distt Dungarpur] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_5]</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>3,06,80,000</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>30680000</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SZsTEje51qysdt9eVkLvAaA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>60</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>299.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>23-Jul-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[Construction of Police station building at Januthar Distt Deeg. ] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_6]</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>3,05,74,000</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>30574000</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SeiwOPN0Q9AfFa4q0d0HBcw%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>60</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>300.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>23-Jul-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[Construction of Police station Building at Chourashi in district Dungarpur] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_7]</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>3,05,00,000</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>30500000</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SAiilRqcj30%2BVXlFHowIJsQ%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>60</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>301.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>23-Jul-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[Remaining work for construction of Police Station Building at Pahari Disttt. Bharatpur] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_8]</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1,76,65,000</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>17665000</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SivrN%2B%2BGQc4lszerKDwzJCA%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Rajasthan eProcurement</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>60</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>302.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>01-Jul-2026 02:00 PM</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>22-Jul-2026 06:00 PM</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>23-Jul-2026 01:00 PM</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[Remaining work of Police station Building at Itawa in district Kota] [RPIDCL/NIT-10/2026-27/D-1835 Dt. 29.06.2026][2026_RPHCC_571762_9]</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>RAJASTHAN POLICE HOUSING AND CONSTRUCTION CORP. LTD.||MANAGING DIRECTOR||GENERAL MANAGER</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1,67,35,000</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>16735000</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://eproc.rajasthan.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=SISTXtJy2gLusBA%2FoSCGfVg%3D%3D</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Best Tender</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Himachal eTenders</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>55</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>46.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>02-Jul-2026 09:00 AM</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 10:30 AM</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>08-Jul-2026 11:00 AM</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[Construction of Heliport at Rora Tehsil Haroli Distt.Una SH C/o Building portion, WS and SI, Safety tank, Rain water harvesting tank, Heliport, Site development, overhead tank, Hanger, watch Tower, Security hut and approach road, providing E.I. Fire ] [Job1 Construction of Heliport at Rora Tehsil Haroli Distt.Una SH C/o Building portion, WS and SI, Sa][2026_PWD_137756_1]</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>PWD</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>14,39,13,728</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>143913728</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://hptenders.gov.in/nicgep/app?component=%24DirectLink&amp;page=FrontEndLatestActiveTenders&amp;service=direct&amp;session=T&amp;sp=Sc1jGj5kxAFe9wiyhRytfLw%3D%3D</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
